--- a/Testing/Answer Keys/iMicroSeq_AnswerKey_S2_Drinking-Source-Water_v1.2.xlsx
+++ b/Testing/Answer Keys/iMicroSeq_AnswerKey_S2_Drinking-Source-Water_v1.2.xlsx
@@ -1770,12 +1770,12 @@
       </c>
       <c r="Q3" s="18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="R3" s="18" t="inlineStr">
         <is>
-          <t>Minute [UO:0000031]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="S3" s="18" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="AA3" s="18" t="inlineStr">
         <is>
-          <t>Bag filtration device [GENEPIO:0102027]</t>
+          <t>Bottle [ENVO:03501326]</t>
         </is>
       </c>
       <c r="AB3" s="18" t="inlineStr">
         <is>
-          <t>Bag Mediated Filtration [GENEPIO:0102028]</t>
+          <t>Grab sampling [GENEPIO:0100953]</t>
         </is>
       </c>
       <c r="AC3" s="18" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="AP3" s="18" t="inlineStr">
         <is>
-          <t>10 L passed through a bag-mediated filtration unit in the field; filter transported on ice and extracted the same evening.</t>
+          <t>1 L grab sample collected at the well head and filtered on a 0.22 um membrane at the laboratory the same evening.</t>
         </is>
       </c>
       <c r="AQ3" s="18" t="inlineStr">
         <is>
-          <t>NWS-SOP-02 Bag-mediated filtration for small drinking water systems</t>
+          <t>NWS-SOP-02 Grab sampling and filtration for small drinking water systems</t>
         </is>
       </c>
       <c r="AR3" s="18" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AS3" s="18" t="inlineStr">
         <is>
-          <t>Field blank of molecular-grade water processed through a clean bag filter at each point.</t>
+          <t>Field blank of molecular-grade water carried to each site and filtered alongside the samples.</t>
         </is>
       </c>
       <c r="AT3" s="18" t="inlineStr">
@@ -2022,7 +2022,7 @@
       <c r="BX3" s="18" t="n"/>
       <c r="BY3" s="18" t="inlineStr">
         <is>
-          <t>Bacteroides HF183 [GENEPIO:0101000]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="BZ3" s="18" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="Q4" s="18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="R4" s="18" t="inlineStr">
         <is>
-          <t>Minute [UO:0000031]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="S4" s="18" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="AA4" s="18" t="inlineStr">
         <is>
-          <t>Bag filtration device [GENEPIO:0102027]</t>
+          <t>Bottle [ENVO:03501326]</t>
         </is>
       </c>
       <c r="AB4" s="18" t="inlineStr">
         <is>
-          <t>Bag Mediated Filtration [GENEPIO:0102028]</t>
+          <t>Grab sampling [GENEPIO:0100953]</t>
         </is>
       </c>
       <c r="AC4" s="18" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="AP4" s="18" t="inlineStr">
         <is>
-          <t>10 L of chlorinated water passed through a bag-mediated filtration unit at the treatment skid outlet; sodium thiosulfate added to quench residual chlorine.</t>
+          <t>1 L grab sample of chlorinated water leaving the chlorination unit, filtered on a 0.22 um membrane the same evening.</t>
         </is>
       </c>
       <c r="AQ4" s="18" t="inlineStr">
         <is>
-          <t>NWS-SOP-02 Bag-mediated filtration for small drinking water systems</t>
+          <t>NWS-SOP-02 Grab sampling and filtration for small drinking water systems</t>
         </is>
       </c>
       <c r="AR4" s="18" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="AS4" s="18" t="inlineStr">
         <is>
-          <t>Field blank of molecular-grade water processed through a clean bag filter at each point.</t>
+          <t>Field blank of molecular-grade water carried to each site and filtered alongside the samples.</t>
         </is>
       </c>
       <c r="AT4" s="18" t="inlineStr">
@@ -2631,7 +2631,7 @@
       <c r="BX4" s="18" t="n"/>
       <c r="BY4" s="18" t="inlineStr">
         <is>
-          <t>Bacteroides HF183 [GENEPIO:0101000]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="BZ4" s="18" t="inlineStr">
@@ -2916,12 +2916,12 @@
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>NWS-TAP-2026-06-04</t>
+          <t>NWS-TANK-2026-06-04</t>
         </is>
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>NWS-DIST-TAP-07</t>
+          <t>NWS-TREATED-TANK-01</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="Q5" s="18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="R5" s="18" t="inlineStr">
         <is>
-          <t>Minute [UO:0000031]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="S5" s="18" t="inlineStr">
@@ -3028,22 +3028,22 @@
       </c>
       <c r="Y5" s="18" t="inlineStr">
         <is>
-          <t>Residential building [ENVO:01000933]</t>
+          <t>Water tank [ENVO:03501254]</t>
         </is>
       </c>
       <c r="Z5" s="18" t="inlineStr">
         <is>
-          <t>Plumbing drain [ENVO:01000924]</t>
+          <t>Drinking water treatment plant [ENVO:03600004]</t>
         </is>
       </c>
       <c r="AA5" s="18" t="inlineStr">
         <is>
-          <t>Bag filtration device [GENEPIO:0102027]</t>
+          <t>Bottle [ENVO:03501326]</t>
         </is>
       </c>
       <c r="AB5" s="18" t="inlineStr">
         <is>
-          <t>Bag Mediated Filtration [GENEPIO:0102028]</t>
+          <t>Grab sampling [GENEPIO:0100953]</t>
         </is>
       </c>
       <c r="AC5" s="18" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="AP5" s="18" t="inlineStr">
         <is>
-          <t>10 L drawn from a cold kitchen tap at the far end of the distribution main after 2 min flushing; bag-mediated filtration on site.</t>
+          <t>1 L grab sample from the community treated water storage tank, filtered on a 0.22 um membrane the same evening.</t>
         </is>
       </c>
       <c r="AQ5" s="18" t="inlineStr">
         <is>
-          <t>NWS-SOP-02 Bag-mediated filtration for small drinking water systems</t>
+          <t>NWS-SOP-02 Grab sampling and filtration for small drinking water systems</t>
         </is>
       </c>
       <c r="AR5" s="18" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AS5" s="18" t="inlineStr">
         <is>
-          <t>Field blank of molecular-grade water processed through a clean bag filter at each point.</t>
+          <t>Field blank of molecular-grade water carried to each site and filtered alongside the samples.</t>
         </is>
       </c>
       <c r="AT5" s="18" t="inlineStr">
@@ -3240,7 +3240,7 @@
       <c r="BX5" s="18" t="n"/>
       <c r="BY5" s="18" t="inlineStr">
         <is>
-          <t>Bacteroides HF183 [GENEPIO:0101000]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="BZ5" s="18" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="DN5" s="18" t="inlineStr">
         <is>
-          <t>Minor quality control issues identified [GENEPIO:0100565]</t>
+          <t>Sequence passed quality control [GENEPIO:0100563]</t>
         </is>
       </c>
       <c r="DO5" s="18" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Minute [UO:0000031]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Bag filtration device [GENEPIO:0102027]</t>
+          <t>Bottle [ENVO:03501326]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Bag Mediated Filtration [GENEPIO:0102028]</t>
+          <t>Grab sampling [GENEPIO:0100953]</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>10 L passed through a bag-mediated filtration unit in the field; filter transported on ice and extracted the same evening.</t>
+          <t>1 L grab sample collected at the well head and filtered on a 0.22 um membrane at the laboratory the same evening.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>NWS-SOP-02 Bag-mediated filtration for small drinking water systems</t>
+          <t>NWS-SOP-02 Grab sampling and filtration for small drinking water systems</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Field blank of molecular-grade water processed through a clean bag filter at each point.</t>
+          <t>Field blank of molecular-grade water carried to each site and filtered alongside the samples.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>Bacteroides HF183 [GENEPIO:0101000]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Minute [UO:0000031]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Bag filtration device [GENEPIO:0102027]</t>
+          <t>Bottle [ENVO:03501326]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Bag Mediated Filtration [GENEPIO:0102028]</t>
+          <t>Grab sampling [GENEPIO:0100953]</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>10 L of chlorinated water passed through a bag-mediated filtration unit at the treatment skid outlet; sodium thiosulfate added to quench residual chlorine.</t>
+          <t>1 L grab sample of chlorinated water leaving the chlorination unit, filtered on a 0.22 um membrane the same evening.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>NWS-SOP-02 Bag-mediated filtration for small drinking water systems</t>
+          <t>NWS-SOP-02 Grab sampling and filtration for small drinking water systems</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Field blank of molecular-grade water processed through a clean bag filter at each point.</t>
+          <t>Field blank of molecular-grade water carried to each site and filtered alongside the samples.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>Bacteroides HF183 [GENEPIO:0101000]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -5615,12 +5615,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NWS-TAP-2026-06-04</t>
+          <t>NWS-TANK-2026-06-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NWS-DIST-TAP-07</t>
+          <t>NWS-TREATED-TANK-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Minute [UO:0000031]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5725,22 +5725,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Residential building [ENVO:01000933]</t>
+          <t>Water tank [ENVO:03501254]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Plumbing drain [ENVO:01000924]</t>
+          <t>Drinking water treatment plant [ENVO:03600004]</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Bag filtration device [GENEPIO:0102027]</t>
+          <t>Bottle [ENVO:03501326]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Bag Mediated Filtration [GENEPIO:0102028]</t>
+          <t>Grab sampling [GENEPIO:0100953]</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10 L drawn from a cold kitchen tap at the far end of the distribution main after 2 min flushing; bag-mediated filtration on site.</t>
+          <t>1 L grab sample from the community treated water storage tank, filtered on a 0.22 um membrane the same evening.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>NWS-SOP-02 Bag-mediated filtration for small drinking water systems</t>
+          <t>NWS-SOP-02 Grab sampling and filtration for small drinking water systems</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Field blank of molecular-grade water processed through a clean bag filter at each point.</t>
+          <t>Field blank of molecular-grade water carried to each site and filtered alongside the samples.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>Bacteroides HF183 [GENEPIO:0101000]</t>
+          <t>Not Applicable [GENEPIO:0001619]</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>Minor quality control issues identified [GENEPIO:0100565]</t>
+          <t>Sequence passed quality control [GENEPIO:0100563]</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
@@ -6213,6 +6213,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -6223,10 +6224,11 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Small-system drinking water investigation triggered by a community observation. Exercises: groundwater and well environmental sites, drinking water environmental material, bag-mediated filtration, community-triggered purpose of sampling and observation presampling activities, 16S amplicon sequencing, and data governance-sensitive fields handled with 'Restricted Access'.</t>
+          <t>Small-system drinking water investigation triggered by a community observation. Exercises: groundwater and well environmental sites, drinking water environmental material, grab sampling in bottles with laboratory filtration, community-triggered purpose of sampling and observation presampling activities, 16S amplicon sequencing, and data governance-sensitive fields handled with 'Restricted Access'.</t>
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
@@ -6241,20 +6243,23 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Land guardians reported discoloured water at two households on 2026-06-02. Sampling took place on 2026-06-04 at three points: the source well head, the treated water leaving the chlorination unit, and a household tap at the far end of the distribution main.</t>
+          <t>Land guardians reported discoloured water at two households on 2026-06-02. Sampling took place on 2026-06-04 at three points: the source well head, the treated water leaving the chlorination unit, and the community treated water storage tank.</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Ten litres per point were processed by bag-mediated filtration in the field; filters were transported on ice and extracted the same evening. Total coliforms and E. coli were enumerated by Colilert (MPN/100 mL). 16S rRNA V3-V4 amplicon sequencing was performed on an Illumina MiSeq, with taxonomic assignment against SILVA 138.2 using QIIME 2.</t>
+          <t>One litre was collected in a sterile bottle at each point as a grab sample; samples were transported on ice and filtered on a 0.22 um membrane at the laboratory the same evening. Total coliforms and E. coli were enumerated by Colilert (MPN/100 mL). 16S rRNA V3-V4 amplicon sequencing was performed on an Illumina MiSeq, with taxonomic assignment against SILVA 138.2 using QIIME 2.</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -6262,6 +6267,8 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
@@ -6283,6 +6290,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
